--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRQ 4A Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TRQ 4A Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -544,13 +544,13 @@
         <v>33338.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16292.6</v>
+        <v>16815.42</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>17046.16</v>
+        <v>16523.34</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>48.87</v>
+        <v>50.44</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -559,11 +559,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>642.59</v>
+        <v>368.49</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>13049.4</v>
+        <v>13142.32</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13070.53</v>
+        <v>12977.61</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.96</v>
+        <v>50.32</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>184.77</v>
+        <v>132.83</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19273.19</v>
+        <v>19276.66</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>98223.73</v>
+        <v>98220.25999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.4</v>
+        <v>16.41</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>23-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18585.42</v>
+        <v>18620.77</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15197.97</v>
+        <v>15162.62</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>55.01</v>
+        <v>55.12</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>23-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>49.12</v>
+        <v>37.93</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5612.64</v>
+        <v>5703.73</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>52683.21</v>
+        <v>52592.12</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>91.09</v>
+        <v>0.11</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5648.57</v>
+        <v>6464.77</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5951.51</v>
+        <v>5135.31</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48.69</v>
+        <v>55.73</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>23-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1228.93</v>
+        <v>889.71</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>35.48</v>
+        <v>59.69</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2908.34</v>
+        <v>2884.14</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.21</v>
+        <v>2.03</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>50.77</v>
+        <v>26.56</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>93.97</v>
+        <v>6513.92</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>12667.35</v>
+        <v>6247.4</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.74</v>
+        <v>51.04</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1237,11 +1237,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23-07-2026</t>
+          <t>24-07-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>6419.95</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -544,13 +544,13 @@
         <v>33338.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16815.42</v>
+        <v>17065.95</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16523.34</v>
+        <v>16272.81</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>50.44</v>
+        <v>51.19</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -559,11 +559,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>368.49</v>
+        <v>524.98</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>13142.32</v>
+        <v>13275.15</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12977.61</v>
+        <v>12844.78</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50.32</v>
+        <v>50.82</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>132.83</v>
+        <v>117.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18620.77</v>
+        <v>18634.53</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15162.62</v>
+        <v>15148.86</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>55.12</v>
+        <v>55.16</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>37.93</v>
+        <v>75.86</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.11</v>
+        <v>878.88</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6464.77</v>
+        <v>7071.49</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5135.31</v>
+        <v>4528.59</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>55.73</v>
+        <v>60.96</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>889.71</v>
+        <v>566.42</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.69</v>
+        <v>86.25</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2884.14</v>
+        <v>2857.58</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.03</v>
+        <v>2.93</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>27-07-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>26.56</v>
+        <v>21.96</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -544,13 +544,13 @@
         <v>33338.76</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>17065.95</v>
+        <v>33338.76</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>16272.81</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.19</v>
+        <v>100</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -559,11 +559,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-07-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>524.98</v>
+        <v>3176.05</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>13275.15</v>
+        <v>15551.44</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12844.78</v>
+        <v>10568.49</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50.82</v>
+        <v>59.54</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-07-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>117.1</v>
+        <v>1424.51</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19276.66</v>
+        <v>19291.28</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>98220.25999999999</v>
+        <v>98205.64</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.41</v>
+        <v>16.42</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>30-07-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>24.93</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18634.53</v>
+        <v>18718.24</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15148.86</v>
+        <v>15065.15</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>55.16</v>
+        <v>55.41</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>27-07-2026</t>
+          <t>30-07-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>75.86</v>
+        <v>6.64</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>30-07-2026</t>
         </is>
       </c>
       <c r="M6" t="n">
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5703.73</v>
+        <v>7825.78</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>52592.12</v>
+        <v>50470.07</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9.779999999999999</v>
+        <v>13.42</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>878.88</v>
+        <v>980.86</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>7071.49</v>
+        <v>7994.35</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4528.59</v>
+        <v>3605.73</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>60.96</v>
+        <v>68.92</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>27-07-2026</t>
+          <t>31-07-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>566.42</v>
+        <v>314.17</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>86.25</v>
+        <v>108.21</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2857.58</v>
+        <v>2835.62</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.93</v>
+        <v>3.68</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27-07-2026</t>
+          <t>29-07-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>21.96</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1164,22 +1164,26 @@
         <v>3150.34</v>
       </c>
       <c r="H12" s="2" t="n">
+        <v>55.16</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>3095.18</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>31-07-2026</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
         <v>0</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>3150.34</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>8.470000000000001</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1222,13 +1226,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6513.92</v>
+        <v>6537.05</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6247.4</v>
+        <v>6224.27</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>51.04</v>
+        <v>51.23</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1237,7 +1241,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>24-07-2026</t>
+          <t>29-07-2026</t>
         </is>
       </c>
       <c r="M13" t="n">

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -559,11 +559,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3176.05</v>
+        <v>138.4</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>15551.44</v>
+        <v>16744.02</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10568.49</v>
+        <v>9375.91</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>59.54</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1424.51</v>
+        <v>305.49</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>24.93</v>
+        <v>454.32</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>6.64</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7825.78</v>
+        <v>7925.09</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>50470.07</v>
+        <v>50370.76</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.42</v>
+        <v>13.59</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>980.86</v>
+        <v>1566.14</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>7994.35</v>
+        <v>8181.62</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3605.73</v>
+        <v>3418.46</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>68.92</v>
+        <v>70.53</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>314.17</v>
+        <v>637.01</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>61.61</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>51.42</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3210.62</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -559,11 +559,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>138.4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>16744.02</v>
+        <v>17049.51</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9375.91</v>
+        <v>9070.42</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>65.27</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>305.49</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19291.28</v>
+        <v>19477.39</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>98205.64</v>
+        <v>98019.53</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.42</v>
+        <v>16.58</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>454.32</v>
+        <v>292.98</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18718.24</v>
+        <v>18796.25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15065.15</v>
+        <v>14987.14</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>55.41</v>
+        <v>55.64</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>79.98999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7925.09</v>
+        <v>9491.219999999999</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>50370.76</v>
+        <v>48804.63</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13.59</v>
+        <v>16.28</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1566.14</v>
+        <v>300.71</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>8181.62</v>
+        <v>8702.84</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3418.46</v>
+        <v>2897.24</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>70.53</v>
+        <v>75.02</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>637.01</v>
+        <v>522.46</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>108.21</v>
+        <v>162.53</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2835.62</v>
+        <v>2781.3</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.68</v>
+        <v>5.52</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>29-07-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>61.61</v>
+        <v>11.38</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>51.42</v>
+        <v>59.09</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1226,13 +1226,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>6537.05</v>
+        <v>9747.67</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6224.27</v>
+        <v>3013.65</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>51.23</v>
+        <v>76.38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1241,11 +1241,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29-07-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3210.62</v>
+        <v>28.05</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>62.15</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19477.39</v>
+        <v>19770.37</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>98019.53</v>
+        <v>97726.55</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.58</v>
+        <v>16.83</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>292.98</v>
+        <v>27.61</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18796.25</v>
+        <v>18798.24</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14987.14</v>
+        <v>14985.15</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>55.64</v>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1.99</v>
+        <v>26.73</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9491.219999999999</v>
+        <v>9791.93</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>48804.63</v>
+        <v>48503.92</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16.28</v>
+        <v>16.8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>300.71</v>
+        <v>2207.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>8702.84</v>
+        <v>9377.280000000001</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2897.24</v>
+        <v>2222.8</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>75.02</v>
+        <v>80.84</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>522.46</v>
+        <v>462.01</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>162.53</v>
+        <v>200.27</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2781.3</v>
+        <v>2743.56</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.52</v>
+        <v>6.8</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>11.38</v>
+        <v>78.88</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1164,13 +1164,13 @@
         <v>3150.34</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.16</v>
+        <v>114.26</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3095.18</v>
+        <v>3036.08</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.75</v>
+        <v>3.63</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>31-07-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>59.09</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1226,13 +1226,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9747.67</v>
+        <v>9778.26</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3013.65</v>
+        <v>2983.06</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>76.38</v>
+        <v>76.62</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1241,11 +1241,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>28.05</v>
+        <v>2.81</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>17049.51</v>
+        <v>17054.21</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9070.42</v>
+        <v>9065.719999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>65.27</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>62.15</v>
+        <v>274.75</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19770.37</v>
+        <v>19801.46</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>97726.55</v>
+        <v>97695.46000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.83</v>
+        <v>16.85</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>27.61</v>
+        <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18798.24</v>
+        <v>18828.89</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14985.15</v>
+        <v>14954.5</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>55.64</v>
+        <v>55.73</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>26.73</v>
+        <v>425.88</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>9791.93</v>
+        <v>11999.13</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>48503.92</v>
+        <v>46296.72</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16.8</v>
+        <v>20.58</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2207.2</v>
+        <v>6902.78</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9377.280000000001</v>
+        <v>9618.99</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2222.8</v>
+        <v>1981.09</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>80.84</v>
+        <v>82.92</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>462.01</v>
+        <v>462.32</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>200.27</v>
+        <v>231.32</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2743.56</v>
+        <v>2712.51</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.8</v>
+        <v>7.86</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>78.88</v>
+        <v>47.83</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1226,13 +1226,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9778.26</v>
+        <v>9780.58</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2983.06</v>
+        <v>2980.74</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>76.62</v>
+        <v>76.64</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1241,11 +1241,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2.81</v>
+        <v>5212.23</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>17054.21</v>
+        <v>17111.66</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9065.719999999999</v>
+        <v>9008.27</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>65.29000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>274.75</v>
+        <v>1149.83</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18828.89</v>
+        <v>18880.14</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14954.5</v>
+        <v>14903.25</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>55.73</v>
+        <v>55.89</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>425.88</v>
+        <v>2666.03</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>11999.13</v>
+        <v>18848.29</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46296.72</v>
+        <v>39447.56</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>20.58</v>
+        <v>32.33</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>6902.78</v>
+        <v>418.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9618.99</v>
+        <v>9911.01</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1981.09</v>
+        <v>1689.07</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>82.92</v>
+        <v>85.44</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>462.32</v>
+        <v>422.35</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>231.32</v>
+        <v>279.15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2712.51</v>
+        <v>2664.68</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.86</v>
+        <v>9.48</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>47.83</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1226,13 +1226,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9780.58</v>
+        <v>9783.389999999999</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2980.74</v>
+        <v>2977.93</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>76.64</v>
+        <v>76.66</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1241,11 +1241,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5212.23</v>
+        <v>5232.8</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>17111.66</v>
+        <v>17351.37</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9008.27</v>
+        <v>8768.559999999999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>65.51000000000001</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1149.83</v>
+        <v>910.12</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>31.8</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>18880.14</v>
+        <v>21241.76</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14903.25</v>
+        <v>12541.63</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>55.89</v>
+        <v>62.88</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2666.03</v>
+        <v>376.93</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>18848.29</v>
+        <v>18901.92</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>39447.56</v>
+        <v>39393.93</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>32.33</v>
+        <v>32.42</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>418.9</v>
+        <v>1485.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>9911.01</v>
+        <v>10081.32</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1689.07</v>
+        <v>1518.76</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>85.44</v>
+        <v>86.91</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>422.35</v>
+        <v>387.25</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1226,13 +1226,13 @@
         <v>12761.32</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>9783.389999999999</v>
+        <v>12761.32</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>2977.93</v>
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>76.66</v>
+        <v>100</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1241,11 +1241,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5232.8</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>17351.37</v>
+        <v>18261.49</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>8768.559999999999</v>
+        <v>7858.44</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>66.43000000000001</v>
+        <v>69.91</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>910.12</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19801.46</v>
+        <v>19853.59</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>97695.46000000001</v>
+        <v>97643.33</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.85</v>
+        <v>16.9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>79.45999999999999</v>
+        <v>27.33</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>21241.76</v>
+        <v>21601.27</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12541.63</v>
+        <v>12182.12</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>62.88</v>
+        <v>63.94</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>376.93</v>
+        <v>9098.93</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>18901.92</v>
+        <v>19267.19</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>39393.93</v>
+        <v>39028.66</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>32.42</v>
+        <v>33.05</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1485.5</v>
+        <v>1435.08</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10081.32</v>
+        <v>10348.08</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1518.76</v>
+        <v>1252</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>86.91</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>387.25</v>
+        <v>493.07</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1476.86</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19853.59</v>
+        <v>19880.91</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>97643.33</v>
+        <v>97616.00999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.9</v>
+        <v>16.92</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>27.33</v>
+        <v>17.8</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>21601.27</v>
+        <v>21626.54</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12182.12</v>
+        <v>12156.85</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63.94</v>
+        <v>64.02</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9098.93</v>
+        <v>9241.08</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>19267.19</v>
+        <v>20440.33</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>39028.66</v>
+        <v>37855.52</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>33.05</v>
+        <v>35.06</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1435.08</v>
+        <v>271.57</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,26 +978,26 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10348.08</v>
+        <v>10489.27</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1252</v>
+        <v>1110.81</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>89.20999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>493.07</v>
+        <v>461.86</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1241,11 +1241,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>18261.49</v>
+        <v>18330.08</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7858.44</v>
+        <v>7789.85</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>69.91</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1476.86</v>
+        <v>1408.27</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>17.8</v>
+        <v>43.84</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,26 +730,26 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>21626.54</v>
+        <v>30867.62</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12156.85</v>
+        <v>2915.77</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64.02</v>
+        <v>91.37</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>9241.08</v>
+        <v>10.07</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>20440.33</v>
+        <v>20702.27</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37855.52</v>
+        <v>37593.58</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35.06</v>
+        <v>35.51</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>271.57</v>
+        <v>44.93</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10489.27</v>
+        <v>10865.57</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1110.81</v>
+        <v>734.51</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>90.42</v>
+        <v>93.67</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>461.86</v>
+        <v>254.98</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>70.53</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>26.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>18330.08</v>
+        <v>20137.75</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7789.85</v>
+        <v>5982.18</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>70.18000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1408.27</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19880.91</v>
+        <v>19898.71</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>97616.00999999999</v>
+        <v>97598.21000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.92</v>
+        <v>16.94</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>43.84</v>
+        <v>26.04</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>10.07</v>
+        <v>38.08</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>20702.27</v>
+        <v>20727.79</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37593.58</v>
+        <v>37568.06</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35.51</v>
+        <v>35.56</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>44.93</v>
+        <v>517.9299999999999</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10865.57</v>
+        <v>10994.72</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>734.51</v>
+        <v>605.36</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>93.67</v>
+        <v>94.78</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>254.98</v>
+        <v>125.83</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>26.6</v>
+        <v>52.34</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1061.58</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19898.71</v>
+        <v>19924.75</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>97598.21000000001</v>
+        <v>97572.17</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.94</v>
+        <v>16.96</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>26.04</v>
+        <v>473.89</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>30867.62</v>
+        <v>30904.06</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2915.77</v>
+        <v>2879.33</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>91.37</v>
+        <v>91.48</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>38.08</v>
+        <v>28.01</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>20727.79</v>
+        <v>20747.2</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37568.06</v>
+        <v>37548.65</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35.56</v>
+        <v>35.59</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>517.9299999999999</v>
+        <v>1547.62</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10994.72</v>
+        <v>11161.33</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>605.36</v>
+        <v>438.75</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>94.78</v>
+        <v>96.22</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>125.83</v>
+        <v>48.59</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1040,13 +1040,13 @@
         <v>2874.21</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>2803.06</v>
+        <v>2873.59</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>71.15000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>97.52</v>
+        <v>99.98</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1055,11 +1055,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>70.53</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         <v>2943.83</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>279.15</v>
+        <v>2943.83</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2664.68</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>9.48</v>
+        <v>100</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>52.34</v>
+        <v>38.85</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3020.86</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>20137.75</v>
+        <v>20644.24</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5982.18</v>
+        <v>5475.69</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1061.58</v>
+        <v>742.1900000000001</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>19924.75</v>
+        <v>20621.97</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>97572.17</v>
+        <v>96874.95</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16.96</v>
+        <v>17.55</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>473.89</v>
+        <v>23.75</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>30904.06</v>
+        <v>30932.07</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2879.33</v>
+        <v>2851.32</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>91.48</v>
+        <v>91.56</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>28.01</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>20747.2</v>
+        <v>21245.72</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37548.65</v>
+        <v>37050.13</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35.59</v>
+        <v>36.44</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1547.62</v>
+        <v>1610.26</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>48.59</v>
+        <v>132.15</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>38.85</v>
+        <v>13.11</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3020.86</v>
+        <v>3047.11</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>20644.24</v>
+        <v>21386.43</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5475.69</v>
+        <v>4733.5</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>79.04000000000001</v>
+        <v>81.88</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>742.1900000000001</v>
+        <v>37.76</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20621.97</v>
+        <v>20639.61</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>96874.95</v>
+        <v>96857.31</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.55</v>
+        <v>17.57</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>23.75</v>
+        <v>345.33</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>21245.72</v>
+        <v>23484.9</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37050.13</v>
+        <v>34810.95</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36.44</v>
+        <v>40.29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1610.26</v>
+        <v>194.12</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11161.33</v>
+        <v>11209.92</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>438.75</v>
+        <v>390.16</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>96.22</v>
+        <v>96.64</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>132.15</v>
+        <v>182.03</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1117,11 +1117,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>13.11</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1164,13 +1164,13 @@
         <v>3150.34</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>114.26</v>
+        <v>3150.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3036.08</v>
+        <v>0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.63</v>
+        <v>100</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3047.11</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>21386.43</v>
+        <v>21410.82</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4733.5</v>
+        <v>4709.11</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>81.88</v>
+        <v>81.97</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>37.76</v>
+        <v>13.37</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20639.61</v>
+        <v>20708.57</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>96857.31</v>
+        <v>96788.35000000001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.57</v>
+        <v>17.62</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>345.33</v>
+        <v>302.37</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>23484.9</v>
+        <v>23972.16</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34810.95</v>
+        <v>34323.69</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>40.29</v>
+        <v>41.12</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>194.12</v>
+        <v>214.02</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11209.92</v>
+        <v>11299.41</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>390.16</v>
+        <v>300.67</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>96.64</v>
+        <v>97.41</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>182.03</v>
+        <v>148.94</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -606,13 +606,13 @@
         <v>26119.93</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>21410.82</v>
+        <v>21424.19</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4709.11</v>
+        <v>4695.74</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>81.97</v>
+        <v>82.02</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -621,11 +621,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>13.37</v>
+        <v>2.06</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20708.57</v>
+        <v>20984.94</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>96788.35000000001</v>
+        <v>96511.98</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.62</v>
+        <v>17.86</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>302.37</v>
+        <v>60.32</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -730,13 +730,13 @@
         <v>33783.39</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>30932.07</v>
+        <v>30937.09</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2851.32</v>
+        <v>2846.3</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>91.56</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -745,11 +745,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>23972.16</v>
+        <v>24005.17</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34323.69</v>
+        <v>34290.68</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41.12</v>
+        <v>41.18</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>214.02</v>
+        <v>207.63</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11299.41</v>
+        <v>11417.33</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>300.67</v>
+        <v>182.75</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>97.41</v>
+        <v>98.42</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>148.94</v>
+        <v>56.13</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>

--- a/public/data/eu-steel-trq-4a-dashboard.xlsx
+++ b/public/data/eu-steel-trq-4a-dashboard.xlsx
@@ -668,13 +668,13 @@
         <v>117496.92</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>20984.94</v>
+        <v>21010.94</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>96511.98</v>
+        <v>96485.98</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17.86</v>
+        <v>17.88</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -683,11 +683,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>60.32</v>
+        <v>55.91</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -854,13 +854,13 @@
         <v>58295.85</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>24005.17</v>
+        <v>24757.28</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34290.68</v>
+        <v>33538.57</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>41.18</v>
+        <v>42.47</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>207.63</v>
+        <v>382.91</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         <v>11600.08</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>11417.33</v>
+        <v>11454.32</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>182.75</v>
+        <v>145.76</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>98.42</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -993,11 +993,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>56.13</v>
+        <v>44.09</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
